--- a/resultats/analyse_complete.xlsx
+++ b/resultats/analyse_complete.xlsx
@@ -14331,7 +14331,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>465.4414973164765</v>
+        <v>465.4414973164764</v>
       </c>
       <c r="C4" t="n">
         <v>0.2570349063927031</v>
